--- a/A18.xlsx
+++ b/A18.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oskar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c126945bea7d3965/UNI/AP1/GitHub/AP1-Gruppe-143/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63A7C01-6F25-4156-8316-916C8276DE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C63A7C01-6F25-4156-8316-916C8276DE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88ECBCDC-698F-4458-A217-2DED1C475ADF}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="30648" windowHeight="18517" xr2:uid="{69F35491-17BF-4D07-9381-CB7802C42E2B}"/>
   </bookViews>
@@ -129,12 +129,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2219,16 +2218,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>43401</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>40607</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19766</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>111509</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>266075</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>18088</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47460</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>88990</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2269,7 +2268,7 @@
     <tableColumn id="4" xr3:uid="{4D665C49-FB0B-419A-B8A9-97AD5C6C3A0F}" name="Periodendauer 1">
       <calculatedColumnFormula>C16/(5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A8045DE8-379B-4364-9397-DFEC80BCF029}" name="Periodendauer 2" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{A8045DE8-379B-4364-9397-DFEC80BCF029}" name="Periodendauer 2" dataDxfId="3">
       <calculatedColumnFormula>ROUND(D16/(5),8)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{0EC4954A-0954-46C8-AD2E-EE1C9D2FD9C4}" name="Spalte1"/>
@@ -2293,10 +2292,10 @@
     <tableColumn id="3" xr3:uid="{914093F1-330D-435D-8583-AE30C98432B9}" name="Periodendauer">
       <calculatedColumnFormula>C31/5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FAABFD4D-E5C0-405A-A8F4-6E6BA3D72BD4}" name="phi (°)" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{FAABFD4D-E5C0-405A-A8F4-6E6BA3D72BD4}" name="phi (°)" dataDxfId="2">
       <calculatedColumnFormula>DEGREES(ASIN(B31/1329))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BD4FFCD2-F927-4E34-B6C5-6D50A53EE661}" name="phi ^2 (°^2)" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{BD4FFCD2-F927-4E34-B6C5-6D50A53EE661}" name="phi ^2 (°^2)" dataDxfId="1">
       <calculatedColumnFormula>Tabelle4[[#This Row],[phi (°)]]^2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{FD69593C-BB0F-4421-9A30-A8C85949CFA3}" name="/16" dataDxfId="0">
@@ -2855,15 +2854,15 @@
         <v>9.9</v>
       </c>
       <c r="E16">
-        <f>C16/(5)</f>
+        <f t="shared" ref="E16:E25" si="3">C16/(5)</f>
         <v>1.986</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F16:F25" si="3">ROUND(D16/(5),8)</f>
+        <f t="shared" ref="F16:F25" si="4">ROUND(D16/(5),8)</f>
         <v>1.98</v>
       </c>
       <c r="H16">
-        <f>C16-D16</f>
+        <f t="shared" ref="H16:H25" si="5">C16-D16</f>
         <v>2.9999999999999361E-2</v>
       </c>
     </row>
@@ -2878,15 +2877,15 @@
         <v>9.89</v>
       </c>
       <c r="E17">
-        <f>C17/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.982</v>
       </c>
       <c r="F17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.978</v>
       </c>
       <c r="H17">
-        <f>C17-D17</f>
+        <f t="shared" si="5"/>
         <v>1.9999999999999574E-2</v>
       </c>
     </row>
@@ -2901,15 +2900,15 @@
         <v>9.8800000000000008</v>
       </c>
       <c r="E18">
-        <f>C18/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.98</v>
       </c>
       <c r="F18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.976</v>
       </c>
       <c r="H18">
-        <f>C18-D18</f>
+        <f t="shared" si="5"/>
         <v>1.9999999999999574E-2</v>
       </c>
     </row>
@@ -2924,15 +2923,15 @@
         <v>9.8699999999999992</v>
       </c>
       <c r="E19">
-        <f>C19/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.9760000000000002</v>
       </c>
       <c r="F19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.974</v>
       </c>
       <c r="H19">
-        <f>C19-D19</f>
+        <f t="shared" si="5"/>
         <v>1.0000000000001563E-2</v>
       </c>
     </row>
@@ -2947,15 +2946,15 @@
         <v>9.86</v>
       </c>
       <c r="E20">
-        <f>C20/(5)</f>
-        <v>1.972</v>
-      </c>
-      <c r="F20">
         <f t="shared" si="3"/>
         <v>1.972</v>
       </c>
+      <c r="F20">
+        <f t="shared" si="4"/>
+        <v>1.972</v>
+      </c>
       <c r="H20">
-        <f>C20-D20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2970,15 +2969,15 @@
         <v>9.85</v>
       </c>
       <c r="E21">
-        <f>C21/(5)</f>
-        <v>1.97</v>
-      </c>
-      <c r="F21">
         <f t="shared" si="3"/>
         <v>1.97</v>
       </c>
+      <c r="F21">
+        <f t="shared" si="4"/>
+        <v>1.97</v>
+      </c>
       <c r="H21">
-        <f>C21-D21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -2993,15 +2992,15 @@
         <v>9.85</v>
       </c>
       <c r="E22">
-        <f>C22/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.968</v>
       </c>
       <c r="F22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.97</v>
       </c>
       <c r="H22">
-        <f>C22-D22</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
     </row>
@@ -3016,15 +3015,15 @@
         <v>9.85</v>
       </c>
       <c r="E23">
-        <f>C23/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.968</v>
       </c>
       <c r="F23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.97</v>
       </c>
       <c r="H23">
-        <f>C23-D23</f>
+        <f t="shared" si="5"/>
         <v>-9.9999999999997868E-3</v>
       </c>
     </row>
@@ -3039,15 +3038,15 @@
         <v>9.85</v>
       </c>
       <c r="E24">
-        <f>C24/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.964</v>
       </c>
       <c r="F24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.97</v>
       </c>
       <c r="H24">
-        <f>C24-D24</f>
+        <f t="shared" si="5"/>
         <v>-2.9999999999999361E-2</v>
       </c>
     </row>
@@ -3062,15 +3061,15 @@
         <v>9.83</v>
       </c>
       <c r="E25">
-        <f>C25/(5)</f>
+        <f t="shared" si="3"/>
         <v>1.954</v>
       </c>
       <c r="F25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.966</v>
       </c>
       <c r="H25">
-        <f>C25-D25</f>
+        <f t="shared" si="5"/>
         <v>-6.0000000000000497E-2</v>
       </c>
     </row>
@@ -3107,11 +3106,11 @@
         <v>9.85</v>
       </c>
       <c r="D31">
-        <f>C31/5</f>
+        <f t="shared" ref="D31:D44" si="6">C31/5</f>
         <v>1.97</v>
       </c>
       <c r="E31">
-        <f>DEGREES(ASIN(B31/1329))</f>
+        <f t="shared" ref="E31:E44" si="7">DEGREES(ASIN(B31/1329))</f>
         <v>2.1129643811228269</v>
       </c>
       <c r="F31">
@@ -3131,11 +3130,11 @@
         <v>9.85</v>
       </c>
       <c r="D32">
-        <f>C32/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
       <c r="E32">
-        <f>DEGREES(ASIN(B32/1329))</f>
+        <f t="shared" si="7"/>
         <v>2.5444412130256069</v>
       </c>
       <c r="F32">
@@ -3155,11 +3154,11 @@
         <v>9.85</v>
       </c>
       <c r="D33">
-        <f>C33/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
       <c r="E33">
-        <f>DEGREES(ASIN(B33/1329))</f>
+        <f t="shared" si="7"/>
         <v>2.9760624902242001</v>
       </c>
       <c r="F33">
@@ -3179,11 +3178,11 @@
         <v>9.85</v>
       </c>
       <c r="D34">
-        <f>C34/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
       <c r="E34">
-        <f>DEGREES(ASIN(B34/1329))</f>
+        <f t="shared" si="7"/>
         <v>3.4078528791493263</v>
       </c>
       <c r="F34">
@@ -3203,11 +3202,11 @@
         <v>9.85</v>
       </c>
       <c r="D35">
-        <f>C35/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
       <c r="E35">
-        <f>DEGREES(ASIN(B35/1329))</f>
+        <f t="shared" si="7"/>
         <v>3.839837133042856</v>
       </c>
       <c r="F35">
@@ -3227,11 +3226,11 @@
         <v>9.86</v>
       </c>
       <c r="D36">
-        <f>C36/5</f>
+        <f t="shared" si="6"/>
         <v>1.972</v>
       </c>
       <c r="E36">
-        <f>DEGREES(ASIN(B36/1329))</f>
+        <f t="shared" si="7"/>
         <v>4.7044867604805729</v>
       </c>
       <c r="F36">
@@ -3251,11 +3250,11 @@
         <v>9.86</v>
       </c>
       <c r="D37">
-        <f>C37/5</f>
+        <f t="shared" si="6"/>
         <v>1.972</v>
       </c>
       <c r="E37">
-        <f>DEGREES(ASIN(B37/1329))</f>
+        <f t="shared" si="7"/>
         <v>5.1372021916683543</v>
       </c>
       <c r="F37">
@@ -3275,11 +3274,11 @@
         <v>9.85</v>
       </c>
       <c r="D38">
-        <f>C38/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
-      <c r="E38" s="2">
-        <f>DEGREES(ASIN(B38/1329))</f>
+      <c r="E38">
+        <f t="shared" si="7"/>
         <v>5.5702116297656641</v>
       </c>
       <c r="F38">
@@ -3299,11 +3298,11 @@
         <v>9.85</v>
       </c>
       <c r="D39">
-        <f>C39/5</f>
+        <f t="shared" si="6"/>
         <v>1.97</v>
       </c>
-      <c r="E39" s="2">
-        <f>DEGREES(ASIN(B39/1329))</f>
+      <c r="E39">
+        <f t="shared" si="7"/>
         <v>6.0035404591762811</v>
       </c>
       <c r="F39">
@@ -3323,11 +3322,11 @@
         <v>9.86</v>
       </c>
       <c r="D40">
-        <f>C40/5</f>
+        <f t="shared" si="6"/>
         <v>1.972</v>
       </c>
-      <c r="E40" s="2">
-        <f>DEGREES(ASIN(B40/1329))</f>
+      <c r="E40">
+        <f t="shared" si="7"/>
         <v>8.6552710678596672</v>
       </c>
       <c r="F40">
@@ -3347,11 +3346,11 @@
         <v>9.8699999999999992</v>
       </c>
       <c r="D41">
-        <f>C41/5</f>
+        <f t="shared" si="6"/>
         <v>1.9739999999999998</v>
       </c>
-      <c r="E41" s="2">
-        <f>DEGREES(ASIN(B41/1329))</f>
+      <c r="E41">
+        <f t="shared" si="7"/>
         <v>10.403947361892518</v>
       </c>
       <c r="F41">
@@ -3371,11 +3370,11 @@
         <v>9.8800000000000008</v>
       </c>
       <c r="D42">
-        <f>C42/5</f>
+        <f t="shared" si="6"/>
         <v>1.9760000000000002</v>
       </c>
-      <c r="E42" s="2">
-        <f>DEGREES(ASIN(B42/1329))</f>
+      <c r="E42">
+        <f t="shared" si="7"/>
         <v>13.046022238972657</v>
       </c>
       <c r="F42">
@@ -3395,11 +3394,11 @@
         <v>9.89</v>
       </c>
       <c r="D43">
-        <f>C43/5</f>
+        <f t="shared" si="6"/>
         <v>1.9780000000000002</v>
       </c>
-      <c r="E43" s="2">
-        <f>DEGREES(ASIN(B43/1329))</f>
+      <c r="E43">
+        <f t="shared" si="7"/>
         <v>15.269283367793342</v>
       </c>
       <c r="F43">
@@ -3419,11 +3418,11 @@
         <v>9.9</v>
       </c>
       <c r="D44">
-        <f>C44/5</f>
+        <f t="shared" si="6"/>
         <v>1.98</v>
       </c>
-      <c r="E44" s="2">
-        <f>DEGREES(ASIN(B44/1329))</f>
+      <c r="E44">
+        <f t="shared" si="7"/>
         <v>17.516364292521324</v>
       </c>
       <c r="F44">
@@ -3436,7 +3435,6 @@
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E45" s="2"/>
       <c r="G45">
         <f>RADIANS(Tabelle4[[#This Row],[phi ^2 (°^2)]])/16</f>
         <v>0</v>
